--- a/artfynd/A 9593-2026 artfynd.xlsx
+++ b/artfynd/A 9593-2026 artfynd.xlsx
@@ -1124,7 +1124,7 @@
         <v>136195679</v>
       </c>
       <c r="B6" t="n">
-        <v>92098</v>
+        <v>92101</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>136202475</v>
       </c>
       <c r="B7" t="n">
-        <v>92098</v>
+        <v>92101</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo, Johan Råghall, Rashid Kadhim, Sten Svantesson</t>
+          <t>Linnea Ingelsbo, Sten Svantesson, Rashid Kadhim, Johan Råghall</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>

--- a/artfynd/A 9593-2026 artfynd.xlsx
+++ b/artfynd/A 9593-2026 artfynd.xlsx
@@ -1124,7 +1124,7 @@
         <v>136195679</v>
       </c>
       <c r="B6" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>136202475</v>
       </c>
       <c r="B7" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo, Sten Svantesson, Rashid Kadhim, Johan Råghall</t>
+          <t>Linnea Ingelsbo, Johan Råghall, Rashid Kadhim, Sten Svantesson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>

--- a/artfynd/A 9593-2026 artfynd.xlsx
+++ b/artfynd/A 9593-2026 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>136196763</v>
       </c>
       <c r="B3" t="n">
-        <v>83453</v>
+        <v>83455</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>136195679</v>
       </c>
       <c r="B6" t="n">
-        <v>92102</v>
+        <v>92107</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>136202475</v>
       </c>
       <c r="B7" t="n">
-        <v>92102</v>
+        <v>92107</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>136202467</v>
       </c>
       <c r="B9" t="n">
-        <v>79633</v>
+        <v>79635</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>136196766</v>
       </c>
       <c r="B10" t="n">
-        <v>75557</v>
+        <v>75559</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>136195682</v>
       </c>
       <c r="B18" t="n">
-        <v>80590</v>
+        <v>80592</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>136202472</v>
       </c>
       <c r="B19" t="n">
-        <v>80590</v>
+        <v>80592</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>136202478</v>
       </c>
       <c r="B20" t="n">
-        <v>80590</v>
+        <v>80592</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>136202476</v>
       </c>
       <c r="B25" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>136202477</v>
       </c>
       <c r="B34" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>136195683</v>
       </c>
       <c r="B39" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>136196765</v>
       </c>
       <c r="B44" t="n">
-        <v>79946</v>
+        <v>79948</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 9593-2026 artfynd.xlsx
+++ b/artfynd/A 9593-2026 artfynd.xlsx
@@ -1124,7 +1124,7 @@
         <v>136195679</v>
       </c>
       <c r="B6" t="n">
-        <v>92107</v>
+        <v>92109</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>136202475</v>
       </c>
       <c r="B7" t="n">
-        <v>92107</v>
+        <v>92109</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
